--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136848501</v>
+        <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>90844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>742203</v>
+        <v>742224</v>
       </c>
       <c r="R2" t="n">
-        <v>7187050</v>
+        <v>7187222</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>gammal sandtallskog med gott om lavbrunnar. Lite förfallen fruktktopp men i den dåliga lukten fanns även den välbekanta doften av anis/lakrits</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,73 +778,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848501</t>
+          <t>https://artportalen.se/Sighting/136922655</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136848499</v>
+        <v>136922173</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742201</v>
+        <v>742181</v>
       </c>
       <c r="R3" t="n">
-        <v>7187054</v>
+        <v>7186977</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,90 +875,85 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på Gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848499</t>
+          <t>https://artportalen.se/Sighting/136922173</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136848505</v>
+        <v>136922185</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>93427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742186</v>
+        <v>742167</v>
       </c>
       <c r="R4" t="n">
-        <v>7187052</v>
+        <v>7186989</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,90 +985,85 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på Gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848505</t>
+          <t>https://artportalen.se/Sighting/136922185</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136848508</v>
+        <v>136922217</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Burheden , Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742148</v>
+        <v>742133</v>
       </c>
       <c r="R5" t="n">
-        <v>7187055</v>
+        <v>7186977</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1097,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>under en gammal tallåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,33 +1106,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848508</t>
+          <t>https://artportalen.se/Sighting/136922217</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136848518</v>
+        <v>136922232</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>93437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,45 +1141,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742169</v>
+        <v>742133</v>
       </c>
       <c r="R6" t="n">
-        <v>7187083</v>
+        <v>7186977</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1212,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>under en gammal tallåga tillsammans med smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,65 +1221,61 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848518</t>
+          <t>https://artportalen.se/Sighting/136922232</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136848520</v>
+        <v>136848501</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1289,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742192</v>
+        <v>742203</v>
       </c>
       <c r="R7" t="n">
-        <v>7187057</v>
+        <v>7187050</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1327,17 +1321,13 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,7 +1345,1492 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136848501</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136922593</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>742190</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7187198</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922593</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136922795</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>742207</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7187050</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922795</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136848499</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Burheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>742201</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7187054</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på Gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136848499</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136848505</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Burheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>742186</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7187052</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på Gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136848505</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136848508</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Burheden , Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>742148</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7187055</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136848508</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136848518</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Burheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>742169</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7187083</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136848518</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136848520</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Burheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>742192</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7187057</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136848520</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136922741</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>742203</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7187062</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922741</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136922790</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>742207</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7187050</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922790</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136922812</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>742155</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7187068</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922812</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136922822</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>742141</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7187074</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922822</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136922847</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>742118</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7187083</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922847</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136922865</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>742204</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7187081</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922865</t>
         </is>
       </c>
     </row>
@@ -1367,6 +2842,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2831,6 +2831,121 @@
       <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136922865</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136930708</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>742067</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7187023</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>tre fruktkroppar, unken doft som gammalt gummi</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136930708</t>
         </is>
       </c>
     </row>
@@ -2855,6 +2970,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,32 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136922173</v>
+        <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>91117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742181</v>
+        <v>742199</v>
       </c>
       <c r="R3" t="n">
-        <v>7186977</v>
+        <v>7186973</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,12 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,19 +893,19 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922173</t>
+          <t>https://artportalen.se/Sighting/136980703</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136922185</v>
+        <v>136922173</v>
       </c>
       <c r="B4" t="n">
         <v>93427</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742167</v>
+        <v>742181</v>
       </c>
       <c r="R4" t="n">
-        <v>7186989</v>
+        <v>7186977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,16 +1009,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922185</t>
+          <t>https://artportalen.se/Sighting/136922173</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136922217</v>
+        <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742133</v>
+        <v>742167</v>
       </c>
       <c r="R5" t="n">
-        <v>7186977</v>
+        <v>7186989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,11 +1095,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>under en gammal tallåga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1118,22 +1113,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922217</t>
+          <t>https://artportalen.se/Sighting/136922185</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136922232</v>
+        <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>93437</v>
+        <v>92166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742133</v>
+        <v>742026</v>
       </c>
       <c r="R6" t="n">
-        <v>7186977</v>
+        <v>7187025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,17 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>under en gammal tallåga tillsammans med smalfotad taggsvamp</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,63 +1223,67 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922232</t>
+          <t>https://artportalen.se/Sighting/136980868</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136848501</v>
+        <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>93436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742203</v>
+        <v>742124</v>
       </c>
       <c r="R7" t="n">
-        <v>7187050</v>
+        <v>7187216</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,12 +1307,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,55 +1328,55 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848501</t>
+          <t>https://artportalen.se/Sighting/136980891</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136922593</v>
+        <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>93436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1393,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742190</v>
+        <v>742130</v>
       </c>
       <c r="R8" t="n">
-        <v>7187198</v>
+        <v>7187219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,12 +1417,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,50 +1443,50 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922593</t>
+          <t>https://artportalen.se/Sighting/136980899</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136922795</v>
+        <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>93405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1503,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742207</v>
+        <v>742217</v>
       </c>
       <c r="R9" t="n">
-        <v>7187050</v>
+        <v>7187168</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,12 +1527,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,68 +1553,67 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922795</t>
+          <t>https://artportalen.se/Sighting/136980969</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136848499</v>
+        <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742201</v>
+        <v>742133</v>
       </c>
       <c r="R10" t="n">
-        <v>7187054</v>
+        <v>7186977</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1647,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på Gran</t>
+          <t>under en gammal tallåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,33 +1656,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848499</t>
+          <t>https://artportalen.se/Sighting/136922217</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136848505</v>
+        <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>93437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,45 +1691,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>742186</v>
+        <v>742133</v>
       </c>
       <c r="R11" t="n">
-        <v>7187052</v>
+        <v>7186977</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1769,7 +1762,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på Gran</t>
+          <t>under en gammal tallåga tillsammans med smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,79 +1771,79 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848505</t>
+          <t>https://artportalen.se/Sighting/136922232</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136848508</v>
+        <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>90895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Burheden , Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742148</v>
+        <v>742199</v>
       </c>
       <c r="R12" t="n">
-        <v>7187055</v>
+        <v>7186973</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,17 +1867,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,79 +1881,79 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848508</t>
+          <t>https://artportalen.se/Sighting/136980699</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136848518</v>
+        <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>90895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742169</v>
+        <v>742033</v>
       </c>
       <c r="R13" t="n">
-        <v>7187083</v>
+        <v>7187015</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,17 +1977,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,79 +1991,79 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848518</t>
+          <t>https://artportalen.se/Sighting/136980798</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136848520</v>
+        <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>90895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Burheden, Vb</t>
+          <t>Burberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742192</v>
+        <v>742095</v>
       </c>
       <c r="R14" t="n">
-        <v>7187057</v>
+        <v>7187210</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,17 +2087,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,79 +2101,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136848520</t>
+          <t>https://artportalen.se/Sighting/136980881</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136922741</v>
+        <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Burberget, Vb</t>
+          <t>Burheden, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>742203</v>
       </c>
       <c r="R15" t="n">
-        <v>7187062</v>
+        <v>7187050</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2227,76 +2201,71 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922741</t>
+          <t>https://artportalen.se/Sighting/136848501</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136922790</v>
+        <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2304,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742207</v>
+        <v>742190</v>
       </c>
       <c r="R16" t="n">
-        <v>7187050</v>
+        <v>7187198</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,17 +2311,13 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2370,48 +2335,47 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922790</t>
+          <t>https://artportalen.se/Sighting/136922593</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136922812</v>
+        <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2419,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742155</v>
+        <v>742207</v>
       </c>
       <c r="R17" t="n">
-        <v>7187068</v>
+        <v>7187050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,17 +2421,13 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2485,13 +2445,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922812</t>
+          <t>https://artportalen.se/Sighting/136922795</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136922822</v>
+        <v>136848499</v>
       </c>
       <c r="B18" t="n">
         <v>58008</v>
@@ -2530,17 +2490,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Burberget, Vb</t>
+          <t>Burheden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742141</v>
+        <v>742201</v>
       </c>
       <c r="R18" t="n">
-        <v>7187074</v>
+        <v>7187054</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2574,7 +2534,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Ringhack på Gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,24 +2549,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922822</t>
+          <t>https://artportalen.se/Sighting/136848499</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136922847</v>
+        <v>136848505</v>
       </c>
       <c r="B19" t="n">
         <v>58008</v>
@@ -2645,17 +2605,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Burberget, Vb</t>
+          <t>Burheden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742118</v>
+        <v>742186</v>
       </c>
       <c r="R19" t="n">
-        <v>7187083</v>
+        <v>7187052</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2689,7 +2649,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Ringhack på Gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,24 +2664,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922847</t>
+          <t>https://artportalen.se/Sighting/136848505</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136922865</v>
+        <v>136848508</v>
       </c>
       <c r="B20" t="n">
         <v>58008</v>
@@ -2760,17 +2720,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Burberget, Vb</t>
+          <t>Burheden , Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742204</v>
+        <v>742148</v>
       </c>
       <c r="R20" t="n">
-        <v>7187081</v>
+        <v>7187055</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2804,7 +2764,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2819,27 +2779,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136922865</t>
+          <t>https://artportalen.se/Sighting/136848508</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136930708</v>
+        <v>136848518</v>
       </c>
       <c r="B21" t="n">
-        <v>91587</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,44 +2807,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>256703</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Burberget, Vb</t>
+          <t>Burheden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742067</v>
+        <v>742169</v>
       </c>
       <c r="R21" t="n">
-        <v>7187023</v>
+        <v>7187083</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2918,7 +2879,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>tre fruktkroppar, unken doft som gammalt gummi</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,23 +2888,1057 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136848518</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136848520</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Burheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>742192</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7187057</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136848520</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136922741</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>742203</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7187062</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922741</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136922790</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>742207</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7187050</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922790</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136922812</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>742155</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7187068</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922812</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136922822</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>742141</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7187074</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922822</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136922847</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>742118</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7187083</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922847</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136922865</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>742204</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7187081</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922865</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136980944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>742196</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7187205</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136980944</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136930708</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Burberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>742067</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7187023</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>tre fruktkroppar, unken doft som gammalt gummi</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136930708</t>
         </is>
@@ -2971,6 +3966,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90849</v>
+        <v>90855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>90859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90861</v>
+        <v>90874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136848499</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136848505</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>136848508</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136848518</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>136848520</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136922741</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>136922790</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136922812</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>136922822</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>136922847</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>136922865</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>136980944</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136848499</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136848505</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>136848508</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136848518</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>136848520</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136922741</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>136922790</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136922812</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>136922822</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>136922847</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>136922865</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>136980944</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -2482,11 +2482,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2597,11 +2593,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2712,11 +2704,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2827,11 +2815,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2942,11 +2926,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3057,11 +3037,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3172,11 +3148,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3287,11 +3259,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3402,11 +3370,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3517,11 +3481,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3632,11 +3592,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3747,11 +3703,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90876</v>
+        <v>90879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90879</v>
+        <v>90889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136848499</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>136848505</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>136848508</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136848518</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>136848520</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>136922741</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136922790</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136922812</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136922822</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>136922847</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>136922865</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>136980944</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136848499</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>136848505</v>
       </c>
       <c r="B19" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>136848508</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136848518</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>136848520</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>136922741</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136922790</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136922812</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136922822</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>136922847</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>136922865</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>136980944</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90893</v>
+        <v>90898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136848499</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>136848505</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>136848508</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136848518</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>136848520</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>136922741</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136922790</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136922812</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136922822</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>136922847</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>136922865</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>136980944</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90898</v>
+        <v>90909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93494</v>
+        <v>93506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93494</v>
+        <v>93506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136848501</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>90910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922655</v>
       </c>
       <c r="B2" t="n">
-        <v>90910</v>
+        <v>90913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136922173</v>
       </c>
       <c r="B4" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136922185</v>
       </c>
       <c r="B5" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136922217</v>
       </c>
       <c r="B10" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136922232</v>
       </c>
       <c r="B11" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>136922593</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136922795</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93510</v>
+        <v>93511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93510</v>
+        <v>93511</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91659</v>
+        <v>91660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27793-2026 artfynd.xlsx
+++ b/artfynd/A 27793-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136980703</v>
       </c>
       <c r="B3" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136980868</v>
       </c>
       <c r="B6" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136980891</v>
       </c>
       <c r="B7" t="n">
-        <v>93511</v>
+        <v>93514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136980899</v>
       </c>
       <c r="B8" t="n">
-        <v>93511</v>
+        <v>93514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136980969</v>
       </c>
       <c r="B9" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136980699</v>
       </c>
       <c r="B12" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>136980798</v>
       </c>
       <c r="B13" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136980881</v>
       </c>
       <c r="B14" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>136980944</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136930708</v>
       </c>
       <c r="B30" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
